--- a/FlexDays-Leave-Tracker.xlsx
+++ b/FlexDays-Leave-Tracker.xlsx
@@ -898,7 +898,7 @@
     <row r="6" ht="28" customHeight="1">
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">  🚀  FlexDays is launching soon — this tracker is a free taste of what's coming  </t>
+          <t xml:space="preserve">  🚀  FlexDays is launching soon. This tracker is a free taste of what's coming  </t>
         </is>
       </c>
     </row>
@@ -919,14 +919,14 @@
     <row r="10" ht="30" customHeight="1">
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>2.  On the 'Leave Log' tab, add a row each time someone takes leave — pick the employee, type, and status from the dropdowns.</t>
+          <t>2.  On the 'Leave Log' tab, add a row each time someone takes leave. Pick the employee, type, and status from the dropdowns.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>3.  The 'Dashboard' and 'Employees' tabs update automatically — balances, totals, low-balance alerts, and a chart.</t>
+          <t>3.  The 'Dashboard' and 'Employees' tabs update automatically: balances, totals, low-balance alerts, and a chart.</t>
         </is>
       </c>
     </row>
@@ -940,42 +940,42 @@
     <row r="14">
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>• Dashboard — your team's leave at a glance (auto)</t>
+          <t>• Dashboard: your team's leave at a glance (auto)</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>• Employees — allowances + remaining balances (auto)</t>
+          <t>• Employees: allowances + remaining balances (auto)</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>• Leave Log — every leave request, with dropdowns</t>
+          <t>• Leave Log: every leave request, with dropdowns</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="B17" s="7" t="inlineStr">
         <is>
-          <t>• FlexDays (Coming Soon) — what you'll get when the app launches</t>
+          <t>• FlexDays (Coming Soon): what you'll get when the app launches</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t>• Settings — edit your leave types &amp; statuses</t>
+          <t>• Settings: edit your leave types &amp; statuses</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="B20" s="8" t="inlineStr">
         <is>
-          <t>Yellow cells = you fill in. White cells = calculate themselves (don't type over them). The example rows just show the format — delete them.</t>
+          <t>Yellow cells = you fill in. White cells = calculate themselves (don't type over them). The example rows just show the format. Delete them.</t>
         </is>
       </c>
     </row>
@@ -1213,7 +1213,7 @@
     <row r="23" ht="26" customHeight="1">
       <c r="B23" s="26" t="inlineStr">
         <is>
-          <t>🚀 Doing all this by hand? FlexDays does it automatically — launching soon.</t>
+          <t>🚀 Doing all this by hand? FlexDays does it automatically. Launching soon.</t>
         </is>
       </c>
     </row>
@@ -1353,7 +1353,7 @@
       </c>
       <c r="G3" s="8" t="inlineStr">
         <is>
-          <t>FlexDays keeps every balance accurate automatically — and it's launching soon.</t>
+          <t>FlexDays keeps every balance accurate automatically, and it's launching soon.</t>
         </is>
       </c>
     </row>
@@ -12169,7 +12169,7 @@
     <row r="3">
       <c r="B3" s="35" t="inlineStr">
         <is>
-          <t>This spreadsheet is handy — but you'll outgrow it. Here's what FlexDays does for you, automatically.</t>
+          <t>This spreadsheet is handy, but you'll outgrow it. Here's what FlexDays does for you, automatically.</t>
         </is>
       </c>
     </row>
@@ -12212,7 +12212,7 @@
     <row r="8" ht="30" customHeight="1">
       <c r="B8" s="36" t="inlineStr">
         <is>
-          <t>✖  No reminders — things get missed</t>
+          <t>✖  No reminders, so things get missed</t>
         </is>
       </c>
       <c r="C8" s="37" t="inlineStr">
@@ -12331,7 +12331,7 @@
       </c>
       <c r="D1" s="41" t="inlineStr">
         <is>
-          <t>Edit these lists to match your company — they feed the dropdowns in the Leave Log.</t>
+          <t>Edit these lists to match your company. They feed the dropdowns in the Leave Log.</t>
         </is>
       </c>
     </row>
